--- a/assets/template-impor-siswa.xlsx
+++ b/assets/template-impor-siswa.xlsx
@@ -510,35 +510,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z405"/>
+  <dimension ref="A1:Y405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -573,115 +572,110 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Jenjang Tahsin-Tahfizh</t>
+          <t>NISN</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>NISN</t>
+          <t>Tempat Lahir</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Tempat Lahir</t>
+          <t>Tanggal Lahir</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Tanggal Lahir</t>
+          <t>Status Aktif</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Status Aktif</t>
+          <t>Jenis Kelamin</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Jenis Kelamin</t>
+          <t>Agama</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Agama</t>
+          <t>Status dalam Keluarga</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Status dalam Keluarga</t>
+          <t>Anak ke</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Anak ke</t>
+          <t>Alamat Peserta Didik</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Alamat Peserta Didik</t>
+          <t>Nomor Telepon Rumah</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Nomor Telepon Rumah</t>
+          <t>Sekolah Asal</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>Sekolah Asal</t>
+          <t>Diterima di Kelas</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Diterima di Kelas</t>
+          <t>Diterima Tanggal</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Diterima Tanggal</t>
+          <t>Nama Ayah</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>Nama Ayah</t>
+          <t>Nama Ibu</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>Nama Ibu</t>
+          <t>Alamat Orang Tua</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Alamat Orang Tua</t>
+          <t>Pekerjaan Ayah</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>Pekerjaan Ayah</t>
+          <t>Pekerjaan Ibu</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>Pekerjaan Ibu</t>
+          <t>Nama Wali</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>Nama Wali</t>
+          <t>Alamat Wali</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>Alamat Wali</t>
+          <t>Telepon Wali</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>Telepon Wali</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>Pekerjaan Wali</t>
         </is>
@@ -705,103 +699,98 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Iqro</t>
+          <t>0123456789</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>0123456789</t>
+          <t>Depok</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Depok</t>
+          <t>2015-06-12</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>2015-06-12</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Aktif</t>
+          <t>Laki-laki</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Laki-laki</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Islam</t>
+          <t>Anak Kandung</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Anak Kandung</t>
+          <t>1 dari 2 bersaudara</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>1 dari 2 bersaudara</t>
+          <t>Jl. Kenanga No. 5 RT 03/02 Kukusan, Beji, Depok</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Jl. Kenanga No. 5 RT 03/02 Kukusan, Beji, Depok</t>
+          <t>0812-3456-7890</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>0812-3456-7890</t>
+          <t>TK Al-Hikmah</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>TK Al-Hikmah</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>Budi Santoso</t>
         </is>
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Budi Santoso</t>
+          <t>Siti Aminah</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Siti Aminah</t>
+          <t>Jl. Kenanga No. 5 RT 03/02 Kukusan, Beji, Depok</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>Jl. Kenanga No. 5 RT 03/02 Kukusan, Beji, Depok</t>
+          <t>Wiraswasta</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>Wiraswasta</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
           <t>Ibu Rumah Tangga</t>
         </is>
       </c>
+      <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr"/>
       <c r="X4" s="5" t="inlineStr"/>
       <c r="Y4" s="5" t="inlineStr"/>
-      <c r="Z4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -840,8 +829,6 @@
       <c r="V5" s="5" t="inlineStr"/>
       <c r="W5" s="5" t="inlineStr"/>
       <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr"/>
-      <c r="Z5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -869,7 +856,6 @@
       <c r="W6" s="6" t="n"/>
       <c r="X6" s="6" t="n"/>
       <c r="Y6" s="6" t="n"/>
-      <c r="Z6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -897,7 +883,6 @@
       <c r="W7" s="6" t="n"/>
       <c r="X7" s="6" t="n"/>
       <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -925,7 +910,6 @@
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n"/>
       <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -953,7 +937,6 @@
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n"/>
       <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -981,7 +964,6 @@
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n"/>
       <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -1009,7 +991,6 @@
       <c r="W11" s="6" t="n"/>
       <c r="X11" s="6" t="n"/>
       <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -1037,7 +1018,6 @@
       <c r="W12" s="6" t="n"/>
       <c r="X12" s="6" t="n"/>
       <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1065,7 +1045,6 @@
       <c r="W13" s="6" t="n"/>
       <c r="X13" s="6" t="n"/>
       <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -1093,7 +1072,6 @@
       <c r="W14" s="6" t="n"/>
       <c r="X14" s="6" t="n"/>
       <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -1121,7 +1099,6 @@
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="6" t="n"/>
       <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -1149,7 +1126,6 @@
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="6" t="n"/>
       <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1177,7 +1153,6 @@
       <c r="W17" s="6" t="n"/>
       <c r="X17" s="6" t="n"/>
       <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1205,7 +1180,6 @@
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="6" t="n"/>
       <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1233,7 +1207,6 @@
       <c r="W19" s="6" t="n"/>
       <c r="X19" s="6" t="n"/>
       <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1261,7 +1234,6 @@
       <c r="W20" s="6" t="n"/>
       <c r="X20" s="6" t="n"/>
       <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1289,7 +1261,6 @@
       <c r="W21" s="6" t="n"/>
       <c r="X21" s="6" t="n"/>
       <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1317,7 +1288,6 @@
       <c r="W22" s="6" t="n"/>
       <c r="X22" s="6" t="n"/>
       <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1345,7 +1315,6 @@
       <c r="W23" s="6" t="n"/>
       <c r="X23" s="6" t="n"/>
       <c r="Y23" s="6" t="n"/>
-      <c r="Z23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1373,7 +1342,6 @@
       <c r="W24" s="6" t="n"/>
       <c r="X24" s="6" t="n"/>
       <c r="Y24" s="6" t="n"/>
-      <c r="Z24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1401,7 +1369,6 @@
       <c r="W25" s="6" t="n"/>
       <c r="X25" s="6" t="n"/>
       <c r="Y25" s="6" t="n"/>
-      <c r="Z25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1429,7 +1396,6 @@
       <c r="W26" s="6" t="n"/>
       <c r="X26" s="6" t="n"/>
       <c r="Y26" s="6" t="n"/>
-      <c r="Z26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1457,7 +1423,6 @@
       <c r="W27" s="6" t="n"/>
       <c r="X27" s="6" t="n"/>
       <c r="Y27" s="6" t="n"/>
-      <c r="Z27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1485,7 +1450,6 @@
       <c r="W28" s="6" t="n"/>
       <c r="X28" s="6" t="n"/>
       <c r="Y28" s="6" t="n"/>
-      <c r="Z28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1513,7 +1477,6 @@
       <c r="W29" s="6" t="n"/>
       <c r="X29" s="6" t="n"/>
       <c r="Y29" s="6" t="n"/>
-      <c r="Z29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1541,7 +1504,6 @@
       <c r="W30" s="6" t="n"/>
       <c r="X30" s="6" t="n"/>
       <c r="Y30" s="6" t="n"/>
-      <c r="Z30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1569,7 +1531,6 @@
       <c r="W31" s="6" t="n"/>
       <c r="X31" s="6" t="n"/>
       <c r="Y31" s="6" t="n"/>
-      <c r="Z31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1597,7 +1558,6 @@
       <c r="W32" s="6" t="n"/>
       <c r="X32" s="6" t="n"/>
       <c r="Y32" s="6" t="n"/>
-      <c r="Z32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1625,7 +1585,6 @@
       <c r="W33" s="6" t="n"/>
       <c r="X33" s="6" t="n"/>
       <c r="Y33" s="6" t="n"/>
-      <c r="Z33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1653,7 +1612,6 @@
       <c r="W34" s="6" t="n"/>
       <c r="X34" s="6" t="n"/>
       <c r="Y34" s="6" t="n"/>
-      <c r="Z34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1681,7 +1639,6 @@
       <c r="W35" s="6" t="n"/>
       <c r="X35" s="6" t="n"/>
       <c r="Y35" s="6" t="n"/>
-      <c r="Z35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1709,7 +1666,6 @@
       <c r="W36" s="6" t="n"/>
       <c r="X36" s="6" t="n"/>
       <c r="Y36" s="6" t="n"/>
-      <c r="Z36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1737,7 +1693,6 @@
       <c r="W37" s="6" t="n"/>
       <c r="X37" s="6" t="n"/>
       <c r="Y37" s="6" t="n"/>
-      <c r="Z37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1765,7 +1720,6 @@
       <c r="W38" s="6" t="n"/>
       <c r="X38" s="6" t="n"/>
       <c r="Y38" s="6" t="n"/>
-      <c r="Z38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1793,7 +1747,6 @@
       <c r="W39" s="6" t="n"/>
       <c r="X39" s="6" t="n"/>
       <c r="Y39" s="6" t="n"/>
-      <c r="Z39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1821,7 +1774,6 @@
       <c r="W40" s="6" t="n"/>
       <c r="X40" s="6" t="n"/>
       <c r="Y40" s="6" t="n"/>
-      <c r="Z40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1849,7 +1801,6 @@
       <c r="W41" s="6" t="n"/>
       <c r="X41" s="6" t="n"/>
       <c r="Y41" s="6" t="n"/>
-      <c r="Z41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1877,7 +1828,6 @@
       <c r="W42" s="6" t="n"/>
       <c r="X42" s="6" t="n"/>
       <c r="Y42" s="6" t="n"/>
-      <c r="Z42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1905,7 +1855,6 @@
       <c r="W43" s="6" t="n"/>
       <c r="X43" s="6" t="n"/>
       <c r="Y43" s="6" t="n"/>
-      <c r="Z43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1933,7 +1882,6 @@
       <c r="W44" s="6" t="n"/>
       <c r="X44" s="6" t="n"/>
       <c r="Y44" s="6" t="n"/>
-      <c r="Z44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1961,7 +1909,6 @@
       <c r="W45" s="6" t="n"/>
       <c r="X45" s="6" t="n"/>
       <c r="Y45" s="6" t="n"/>
-      <c r="Z45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1989,7 +1936,6 @@
       <c r="W46" s="6" t="n"/>
       <c r="X46" s="6" t="n"/>
       <c r="Y46" s="6" t="n"/>
-      <c r="Z46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -2017,7 +1963,6 @@
       <c r="W47" s="6" t="n"/>
       <c r="X47" s="6" t="n"/>
       <c r="Y47" s="6" t="n"/>
-      <c r="Z47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -2045,7 +1990,6 @@
       <c r="W48" s="6" t="n"/>
       <c r="X48" s="6" t="n"/>
       <c r="Y48" s="6" t="n"/>
-      <c r="Z48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -2073,7 +2017,6 @@
       <c r="W49" s="6" t="n"/>
       <c r="X49" s="6" t="n"/>
       <c r="Y49" s="6" t="n"/>
-      <c r="Z49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -2101,7 +2044,6 @@
       <c r="W50" s="6" t="n"/>
       <c r="X50" s="6" t="n"/>
       <c r="Y50" s="6" t="n"/>
-      <c r="Z50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -2129,7 +2071,6 @@
       <c r="W51" s="6" t="n"/>
       <c r="X51" s="6" t="n"/>
       <c r="Y51" s="6" t="n"/>
-      <c r="Z51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -2157,7 +2098,6 @@
       <c r="W52" s="6" t="n"/>
       <c r="X52" s="6" t="n"/>
       <c r="Y52" s="6" t="n"/>
-      <c r="Z52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -2185,7 +2125,6 @@
       <c r="W53" s="6" t="n"/>
       <c r="X53" s="6" t="n"/>
       <c r="Y53" s="6" t="n"/>
-      <c r="Z53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -2213,7 +2152,6 @@
       <c r="W54" s="6" t="n"/>
       <c r="X54" s="6" t="n"/>
       <c r="Y54" s="6" t="n"/>
-      <c r="Z54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -2241,7 +2179,6 @@
       <c r="W55" s="6" t="n"/>
       <c r="X55" s="6" t="n"/>
       <c r="Y55" s="6" t="n"/>
-      <c r="Z55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -2269,7 +2206,6 @@
       <c r="W56" s="6" t="n"/>
       <c r="X56" s="6" t="n"/>
       <c r="Y56" s="6" t="n"/>
-      <c r="Z56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -2297,7 +2233,6 @@
       <c r="W57" s="6" t="n"/>
       <c r="X57" s="6" t="n"/>
       <c r="Y57" s="6" t="n"/>
-      <c r="Z57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -2325,7 +2260,6 @@
       <c r="W58" s="6" t="n"/>
       <c r="X58" s="6" t="n"/>
       <c r="Y58" s="6" t="n"/>
-      <c r="Z58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -2353,7 +2287,6 @@
       <c r="W59" s="6" t="n"/>
       <c r="X59" s="6" t="n"/>
       <c r="Y59" s="6" t="n"/>
-      <c r="Z59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -2381,7 +2314,6 @@
       <c r="W60" s="6" t="n"/>
       <c r="X60" s="6" t="n"/>
       <c r="Y60" s="6" t="n"/>
-      <c r="Z60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -2409,7 +2341,6 @@
       <c r="W61" s="6" t="n"/>
       <c r="X61" s="6" t="n"/>
       <c r="Y61" s="6" t="n"/>
-      <c r="Z61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -2437,7 +2368,6 @@
       <c r="W62" s="6" t="n"/>
       <c r="X62" s="6" t="n"/>
       <c r="Y62" s="6" t="n"/>
-      <c r="Z62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -2465,7 +2395,6 @@
       <c r="W63" s="6" t="n"/>
       <c r="X63" s="6" t="n"/>
       <c r="Y63" s="6" t="n"/>
-      <c r="Z63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -2493,7 +2422,6 @@
       <c r="W64" s="6" t="n"/>
       <c r="X64" s="6" t="n"/>
       <c r="Y64" s="6" t="n"/>
-      <c r="Z64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -2521,7 +2449,6 @@
       <c r="W65" s="6" t="n"/>
       <c r="X65" s="6" t="n"/>
       <c r="Y65" s="6" t="n"/>
-      <c r="Z65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -2549,7 +2476,6 @@
       <c r="W66" s="6" t="n"/>
       <c r="X66" s="6" t="n"/>
       <c r="Y66" s="6" t="n"/>
-      <c r="Z66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -2577,7 +2503,6 @@
       <c r="W67" s="6" t="n"/>
       <c r="X67" s="6" t="n"/>
       <c r="Y67" s="6" t="n"/>
-      <c r="Z67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -2605,7 +2530,6 @@
       <c r="W68" s="6" t="n"/>
       <c r="X68" s="6" t="n"/>
       <c r="Y68" s="6" t="n"/>
-      <c r="Z68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -2633,7 +2557,6 @@
       <c r="W69" s="6" t="n"/>
       <c r="X69" s="6" t="n"/>
       <c r="Y69" s="6" t="n"/>
-      <c r="Z69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -2661,7 +2584,6 @@
       <c r="W70" s="6" t="n"/>
       <c r="X70" s="6" t="n"/>
       <c r="Y70" s="6" t="n"/>
-      <c r="Z70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -2689,7 +2611,6 @@
       <c r="W71" s="6" t="n"/>
       <c r="X71" s="6" t="n"/>
       <c r="Y71" s="6" t="n"/>
-      <c r="Z71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -2717,7 +2638,6 @@
       <c r="W72" s="6" t="n"/>
       <c r="X72" s="6" t="n"/>
       <c r="Y72" s="6" t="n"/>
-      <c r="Z72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -2745,7 +2665,6 @@
       <c r="W73" s="6" t="n"/>
       <c r="X73" s="6" t="n"/>
       <c r="Y73" s="6" t="n"/>
-      <c r="Z73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -2773,7 +2692,6 @@
       <c r="W74" s="6" t="n"/>
       <c r="X74" s="6" t="n"/>
       <c r="Y74" s="6" t="n"/>
-      <c r="Z74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -2801,7 +2719,6 @@
       <c r="W75" s="6" t="n"/>
       <c r="X75" s="6" t="n"/>
       <c r="Y75" s="6" t="n"/>
-      <c r="Z75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -2829,7 +2746,6 @@
       <c r="W76" s="6" t="n"/>
       <c r="X76" s="6" t="n"/>
       <c r="Y76" s="6" t="n"/>
-      <c r="Z76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -2857,7 +2773,6 @@
       <c r="W77" s="6" t="n"/>
       <c r="X77" s="6" t="n"/>
       <c r="Y77" s="6" t="n"/>
-      <c r="Z77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -2885,7 +2800,6 @@
       <c r="W78" s="6" t="n"/>
       <c r="X78" s="6" t="n"/>
       <c r="Y78" s="6" t="n"/>
-      <c r="Z78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -2913,7 +2827,6 @@
       <c r="W79" s="6" t="n"/>
       <c r="X79" s="6" t="n"/>
       <c r="Y79" s="6" t="n"/>
-      <c r="Z79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -2941,7 +2854,6 @@
       <c r="W80" s="6" t="n"/>
       <c r="X80" s="6" t="n"/>
       <c r="Y80" s="6" t="n"/>
-      <c r="Z80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -2969,7 +2881,6 @@
       <c r="W81" s="6" t="n"/>
       <c r="X81" s="6" t="n"/>
       <c r="Y81" s="6" t="n"/>
-      <c r="Z81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -2997,7 +2908,6 @@
       <c r="W82" s="6" t="n"/>
       <c r="X82" s="6" t="n"/>
       <c r="Y82" s="6" t="n"/>
-      <c r="Z82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -3025,7 +2935,6 @@
       <c r="W83" s="6" t="n"/>
       <c r="X83" s="6" t="n"/>
       <c r="Y83" s="6" t="n"/>
-      <c r="Z83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -3053,7 +2962,6 @@
       <c r="W84" s="6" t="n"/>
       <c r="X84" s="6" t="n"/>
       <c r="Y84" s="6" t="n"/>
-      <c r="Z84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -3081,7 +2989,6 @@
       <c r="W85" s="6" t="n"/>
       <c r="X85" s="6" t="n"/>
       <c r="Y85" s="6" t="n"/>
-      <c r="Z85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -3109,7 +3016,6 @@
       <c r="W86" s="6" t="n"/>
       <c r="X86" s="6" t="n"/>
       <c r="Y86" s="6" t="n"/>
-      <c r="Z86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -3137,7 +3043,6 @@
       <c r="W87" s="6" t="n"/>
       <c r="X87" s="6" t="n"/>
       <c r="Y87" s="6" t="n"/>
-      <c r="Z87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -3165,7 +3070,6 @@
       <c r="W88" s="6" t="n"/>
       <c r="X88" s="6" t="n"/>
       <c r="Y88" s="6" t="n"/>
-      <c r="Z88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -3193,7 +3097,6 @@
       <c r="W89" s="6" t="n"/>
       <c r="X89" s="6" t="n"/>
       <c r="Y89" s="6" t="n"/>
-      <c r="Z89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -3221,7 +3124,6 @@
       <c r="W90" s="6" t="n"/>
       <c r="X90" s="6" t="n"/>
       <c r="Y90" s="6" t="n"/>
-      <c r="Z90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -3249,7 +3151,6 @@
       <c r="W91" s="6" t="n"/>
       <c r="X91" s="6" t="n"/>
       <c r="Y91" s="6" t="n"/>
-      <c r="Z91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -3277,7 +3178,6 @@
       <c r="W92" s="6" t="n"/>
       <c r="X92" s="6" t="n"/>
       <c r="Y92" s="6" t="n"/>
-      <c r="Z92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -3305,7 +3205,6 @@
       <c r="W93" s="6" t="n"/>
       <c r="X93" s="6" t="n"/>
       <c r="Y93" s="6" t="n"/>
-      <c r="Z93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -3333,7 +3232,6 @@
       <c r="W94" s="6" t="n"/>
       <c r="X94" s="6" t="n"/>
       <c r="Y94" s="6" t="n"/>
-      <c r="Z94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -3361,7 +3259,6 @@
       <c r="W95" s="6" t="n"/>
       <c r="X95" s="6" t="n"/>
       <c r="Y95" s="6" t="n"/>
-      <c r="Z95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -3389,7 +3286,6 @@
       <c r="W96" s="6" t="n"/>
       <c r="X96" s="6" t="n"/>
       <c r="Y96" s="6" t="n"/>
-      <c r="Z96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -3417,7 +3313,6 @@
       <c r="W97" s="6" t="n"/>
       <c r="X97" s="6" t="n"/>
       <c r="Y97" s="6" t="n"/>
-      <c r="Z97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -3445,7 +3340,6 @@
       <c r="W98" s="6" t="n"/>
       <c r="X98" s="6" t="n"/>
       <c r="Y98" s="6" t="n"/>
-      <c r="Z98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -3473,7 +3367,6 @@
       <c r="W99" s="6" t="n"/>
       <c r="X99" s="6" t="n"/>
       <c r="Y99" s="6" t="n"/>
-      <c r="Z99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -3501,7 +3394,6 @@
       <c r="W100" s="6" t="n"/>
       <c r="X100" s="6" t="n"/>
       <c r="Y100" s="6" t="n"/>
-      <c r="Z100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -3529,7 +3421,6 @@
       <c r="W101" s="6" t="n"/>
       <c r="X101" s="6" t="n"/>
       <c r="Y101" s="6" t="n"/>
-      <c r="Z101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -3557,7 +3448,6 @@
       <c r="W102" s="6" t="n"/>
       <c r="X102" s="6" t="n"/>
       <c r="Y102" s="6" t="n"/>
-      <c r="Z102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -3585,7 +3475,6 @@
       <c r="W103" s="6" t="n"/>
       <c r="X103" s="6" t="n"/>
       <c r="Y103" s="6" t="n"/>
-      <c r="Z103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -3613,7 +3502,6 @@
       <c r="W104" s="6" t="n"/>
       <c r="X104" s="6" t="n"/>
       <c r="Y104" s="6" t="n"/>
-      <c r="Z104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -3641,7 +3529,6 @@
       <c r="W105" s="6" t="n"/>
       <c r="X105" s="6" t="n"/>
       <c r="Y105" s="6" t="n"/>
-      <c r="Z105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -3669,7 +3556,6 @@
       <c r="W106" s="6" t="n"/>
       <c r="X106" s="6" t="n"/>
       <c r="Y106" s="6" t="n"/>
-      <c r="Z106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -3697,7 +3583,6 @@
       <c r="W107" s="6" t="n"/>
       <c r="X107" s="6" t="n"/>
       <c r="Y107" s="6" t="n"/>
-      <c r="Z107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -3725,7 +3610,6 @@
       <c r="W108" s="6" t="n"/>
       <c r="X108" s="6" t="n"/>
       <c r="Y108" s="6" t="n"/>
-      <c r="Z108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -3753,7 +3637,6 @@
       <c r="W109" s="6" t="n"/>
       <c r="X109" s="6" t="n"/>
       <c r="Y109" s="6" t="n"/>
-      <c r="Z109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -3781,7 +3664,6 @@
       <c r="W110" s="6" t="n"/>
       <c r="X110" s="6" t="n"/>
       <c r="Y110" s="6" t="n"/>
-      <c r="Z110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -3809,7 +3691,6 @@
       <c r="W111" s="6" t="n"/>
       <c r="X111" s="6" t="n"/>
       <c r="Y111" s="6" t="n"/>
-      <c r="Z111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -3837,7 +3718,6 @@
       <c r="W112" s="6" t="n"/>
       <c r="X112" s="6" t="n"/>
       <c r="Y112" s="6" t="n"/>
-      <c r="Z112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -3865,7 +3745,6 @@
       <c r="W113" s="6" t="n"/>
       <c r="X113" s="6" t="n"/>
       <c r="Y113" s="6" t="n"/>
-      <c r="Z113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -3893,7 +3772,6 @@
       <c r="W114" s="6" t="n"/>
       <c r="X114" s="6" t="n"/>
       <c r="Y114" s="6" t="n"/>
-      <c r="Z114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -3921,7 +3799,6 @@
       <c r="W115" s="6" t="n"/>
       <c r="X115" s="6" t="n"/>
       <c r="Y115" s="6" t="n"/>
-      <c r="Z115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -3949,7 +3826,6 @@
       <c r="W116" s="6" t="n"/>
       <c r="X116" s="6" t="n"/>
       <c r="Y116" s="6" t="n"/>
-      <c r="Z116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -3977,7 +3853,6 @@
       <c r="W117" s="6" t="n"/>
       <c r="X117" s="6" t="n"/>
       <c r="Y117" s="6" t="n"/>
-      <c r="Z117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -4005,7 +3880,6 @@
       <c r="W118" s="6" t="n"/>
       <c r="X118" s="6" t="n"/>
       <c r="Y118" s="6" t="n"/>
-      <c r="Z118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -4033,7 +3907,6 @@
       <c r="W119" s="6" t="n"/>
       <c r="X119" s="6" t="n"/>
       <c r="Y119" s="6" t="n"/>
-      <c r="Z119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -4061,7 +3934,6 @@
       <c r="W120" s="6" t="n"/>
       <c r="X120" s="6" t="n"/>
       <c r="Y120" s="6" t="n"/>
-      <c r="Z120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -4089,7 +3961,6 @@
       <c r="W121" s="6" t="n"/>
       <c r="X121" s="6" t="n"/>
       <c r="Y121" s="6" t="n"/>
-      <c r="Z121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -4117,7 +3988,6 @@
       <c r="W122" s="6" t="n"/>
       <c r="X122" s="6" t="n"/>
       <c r="Y122" s="6" t="n"/>
-      <c r="Z122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -4145,7 +4015,6 @@
       <c r="W123" s="6" t="n"/>
       <c r="X123" s="6" t="n"/>
       <c r="Y123" s="6" t="n"/>
-      <c r="Z123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -4173,7 +4042,6 @@
       <c r="W124" s="6" t="n"/>
       <c r="X124" s="6" t="n"/>
       <c r="Y124" s="6" t="n"/>
-      <c r="Z124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -4201,7 +4069,6 @@
       <c r="W125" s="6" t="n"/>
       <c r="X125" s="6" t="n"/>
       <c r="Y125" s="6" t="n"/>
-      <c r="Z125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -4229,7 +4096,6 @@
       <c r="W126" s="6" t="n"/>
       <c r="X126" s="6" t="n"/>
       <c r="Y126" s="6" t="n"/>
-      <c r="Z126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -4257,7 +4123,6 @@
       <c r="W127" s="6" t="n"/>
       <c r="X127" s="6" t="n"/>
       <c r="Y127" s="6" t="n"/>
-      <c r="Z127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -4285,7 +4150,6 @@
       <c r="W128" s="6" t="n"/>
       <c r="X128" s="6" t="n"/>
       <c r="Y128" s="6" t="n"/>
-      <c r="Z128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -4313,7 +4177,6 @@
       <c r="W129" s="6" t="n"/>
       <c r="X129" s="6" t="n"/>
       <c r="Y129" s="6" t="n"/>
-      <c r="Z129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -4341,7 +4204,6 @@
       <c r="W130" s="6" t="n"/>
       <c r="X130" s="6" t="n"/>
       <c r="Y130" s="6" t="n"/>
-      <c r="Z130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -4369,7 +4231,6 @@
       <c r="W131" s="6" t="n"/>
       <c r="X131" s="6" t="n"/>
       <c r="Y131" s="6" t="n"/>
-      <c r="Z131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -4397,7 +4258,6 @@
       <c r="W132" s="6" t="n"/>
       <c r="X132" s="6" t="n"/>
       <c r="Y132" s="6" t="n"/>
-      <c r="Z132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -4425,7 +4285,6 @@
       <c r="W133" s="6" t="n"/>
       <c r="X133" s="6" t="n"/>
       <c r="Y133" s="6" t="n"/>
-      <c r="Z133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -4453,7 +4312,6 @@
       <c r="W134" s="6" t="n"/>
       <c r="X134" s="6" t="n"/>
       <c r="Y134" s="6" t="n"/>
-      <c r="Z134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -4481,7 +4339,6 @@
       <c r="W135" s="6" t="n"/>
       <c r="X135" s="6" t="n"/>
       <c r="Y135" s="6" t="n"/>
-      <c r="Z135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -4509,7 +4366,6 @@
       <c r="W136" s="6" t="n"/>
       <c r="X136" s="6" t="n"/>
       <c r="Y136" s="6" t="n"/>
-      <c r="Z136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -4537,7 +4393,6 @@
       <c r="W137" s="6" t="n"/>
       <c r="X137" s="6" t="n"/>
       <c r="Y137" s="6" t="n"/>
-      <c r="Z137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -4565,7 +4420,6 @@
       <c r="W138" s="6" t="n"/>
       <c r="X138" s="6" t="n"/>
       <c r="Y138" s="6" t="n"/>
-      <c r="Z138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -4593,7 +4447,6 @@
       <c r="W139" s="6" t="n"/>
       <c r="X139" s="6" t="n"/>
       <c r="Y139" s="6" t="n"/>
-      <c r="Z139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -4621,7 +4474,6 @@
       <c r="W140" s="6" t="n"/>
       <c r="X140" s="6" t="n"/>
       <c r="Y140" s="6" t="n"/>
-      <c r="Z140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -4649,7 +4501,6 @@
       <c r="W141" s="6" t="n"/>
       <c r="X141" s="6" t="n"/>
       <c r="Y141" s="6" t="n"/>
-      <c r="Z141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -4677,7 +4528,6 @@
       <c r="W142" s="6" t="n"/>
       <c r="X142" s="6" t="n"/>
       <c r="Y142" s="6" t="n"/>
-      <c r="Z142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -4705,7 +4555,6 @@
       <c r="W143" s="6" t="n"/>
       <c r="X143" s="6" t="n"/>
       <c r="Y143" s="6" t="n"/>
-      <c r="Z143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -4733,7 +4582,6 @@
       <c r="W144" s="6" t="n"/>
       <c r="X144" s="6" t="n"/>
       <c r="Y144" s="6" t="n"/>
-      <c r="Z144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -4761,7 +4609,6 @@
       <c r="W145" s="6" t="n"/>
       <c r="X145" s="6" t="n"/>
       <c r="Y145" s="6" t="n"/>
-      <c r="Z145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -4789,7 +4636,6 @@
       <c r="W146" s="6" t="n"/>
       <c r="X146" s="6" t="n"/>
       <c r="Y146" s="6" t="n"/>
-      <c r="Z146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -4817,7 +4663,6 @@
       <c r="W147" s="6" t="n"/>
       <c r="X147" s="6" t="n"/>
       <c r="Y147" s="6" t="n"/>
-      <c r="Z147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -4845,7 +4690,6 @@
       <c r="W148" s="6" t="n"/>
       <c r="X148" s="6" t="n"/>
       <c r="Y148" s="6" t="n"/>
-      <c r="Z148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -4873,7 +4717,6 @@
       <c r="W149" s="6" t="n"/>
       <c r="X149" s="6" t="n"/>
       <c r="Y149" s="6" t="n"/>
-      <c r="Z149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -4901,7 +4744,6 @@
       <c r="W150" s="6" t="n"/>
       <c r="X150" s="6" t="n"/>
       <c r="Y150" s="6" t="n"/>
-      <c r="Z150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
@@ -4929,7 +4771,6 @@
       <c r="W151" s="6" t="n"/>
       <c r="X151" s="6" t="n"/>
       <c r="Y151" s="6" t="n"/>
-      <c r="Z151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
@@ -4957,7 +4798,6 @@
       <c r="W152" s="6" t="n"/>
       <c r="X152" s="6" t="n"/>
       <c r="Y152" s="6" t="n"/>
-      <c r="Z152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
@@ -4985,7 +4825,6 @@
       <c r="W153" s="6" t="n"/>
       <c r="X153" s="6" t="n"/>
       <c r="Y153" s="6" t="n"/>
-      <c r="Z153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
@@ -5013,7 +4852,6 @@
       <c r="W154" s="6" t="n"/>
       <c r="X154" s="6" t="n"/>
       <c r="Y154" s="6" t="n"/>
-      <c r="Z154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
@@ -5041,7 +4879,6 @@
       <c r="W155" s="6" t="n"/>
       <c r="X155" s="6" t="n"/>
       <c r="Y155" s="6" t="n"/>
-      <c r="Z155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
@@ -5069,7 +4906,6 @@
       <c r="W156" s="6" t="n"/>
       <c r="X156" s="6" t="n"/>
       <c r="Y156" s="6" t="n"/>
-      <c r="Z156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
@@ -5097,7 +4933,6 @@
       <c r="W157" s="6" t="n"/>
       <c r="X157" s="6" t="n"/>
       <c r="Y157" s="6" t="n"/>
-      <c r="Z157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
@@ -5125,7 +4960,6 @@
       <c r="W158" s="6" t="n"/>
       <c r="X158" s="6" t="n"/>
       <c r="Y158" s="6" t="n"/>
-      <c r="Z158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
@@ -5153,7 +4987,6 @@
       <c r="W159" s="6" t="n"/>
       <c r="X159" s="6" t="n"/>
       <c r="Y159" s="6" t="n"/>
-      <c r="Z159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
@@ -5181,7 +5014,6 @@
       <c r="W160" s="6" t="n"/>
       <c r="X160" s="6" t="n"/>
       <c r="Y160" s="6" t="n"/>
-      <c r="Z160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
@@ -5209,7 +5041,6 @@
       <c r="W161" s="6" t="n"/>
       <c r="X161" s="6" t="n"/>
       <c r="Y161" s="6" t="n"/>
-      <c r="Z161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
@@ -5237,7 +5068,6 @@
       <c r="W162" s="6" t="n"/>
       <c r="X162" s="6" t="n"/>
       <c r="Y162" s="6" t="n"/>
-      <c r="Z162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
@@ -5265,7 +5095,6 @@
       <c r="W163" s="6" t="n"/>
       <c r="X163" s="6" t="n"/>
       <c r="Y163" s="6" t="n"/>
-      <c r="Z163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
@@ -5293,7 +5122,6 @@
       <c r="W164" s="6" t="n"/>
       <c r="X164" s="6" t="n"/>
       <c r="Y164" s="6" t="n"/>
-      <c r="Z164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
@@ -5321,7 +5149,6 @@
       <c r="W165" s="6" t="n"/>
       <c r="X165" s="6" t="n"/>
       <c r="Y165" s="6" t="n"/>
-      <c r="Z165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
@@ -5349,7 +5176,6 @@
       <c r="W166" s="6" t="n"/>
       <c r="X166" s="6" t="n"/>
       <c r="Y166" s="6" t="n"/>
-      <c r="Z166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
@@ -5377,7 +5203,6 @@
       <c r="W167" s="6" t="n"/>
       <c r="X167" s="6" t="n"/>
       <c r="Y167" s="6" t="n"/>
-      <c r="Z167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
@@ -5405,7 +5230,6 @@
       <c r="W168" s="6" t="n"/>
       <c r="X168" s="6" t="n"/>
       <c r="Y168" s="6" t="n"/>
-      <c r="Z168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
@@ -5433,7 +5257,6 @@
       <c r="W169" s="6" t="n"/>
       <c r="X169" s="6" t="n"/>
       <c r="Y169" s="6" t="n"/>
-      <c r="Z169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
@@ -5461,7 +5284,6 @@
       <c r="W170" s="6" t="n"/>
       <c r="X170" s="6" t="n"/>
       <c r="Y170" s="6" t="n"/>
-      <c r="Z170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
@@ -5489,7 +5311,6 @@
       <c r="W171" s="6" t="n"/>
       <c r="X171" s="6" t="n"/>
       <c r="Y171" s="6" t="n"/>
-      <c r="Z171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
@@ -5517,7 +5338,6 @@
       <c r="W172" s="6" t="n"/>
       <c r="X172" s="6" t="n"/>
       <c r="Y172" s="6" t="n"/>
-      <c r="Z172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
@@ -5545,7 +5365,6 @@
       <c r="W173" s="6" t="n"/>
       <c r="X173" s="6" t="n"/>
       <c r="Y173" s="6" t="n"/>
-      <c r="Z173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
@@ -5573,7 +5392,6 @@
       <c r="W174" s="6" t="n"/>
       <c r="X174" s="6" t="n"/>
       <c r="Y174" s="6" t="n"/>
-      <c r="Z174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
@@ -5601,7 +5419,6 @@
       <c r="W175" s="6" t="n"/>
       <c r="X175" s="6" t="n"/>
       <c r="Y175" s="6" t="n"/>
-      <c r="Z175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
@@ -5629,7 +5446,6 @@
       <c r="W176" s="6" t="n"/>
       <c r="X176" s="6" t="n"/>
       <c r="Y176" s="6" t="n"/>
-      <c r="Z176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
@@ -5657,7 +5473,6 @@
       <c r="W177" s="6" t="n"/>
       <c r="X177" s="6" t="n"/>
       <c r="Y177" s="6" t="n"/>
-      <c r="Z177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
@@ -5685,7 +5500,6 @@
       <c r="W178" s="6" t="n"/>
       <c r="X178" s="6" t="n"/>
       <c r="Y178" s="6" t="n"/>
-      <c r="Z178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
@@ -5713,7 +5527,6 @@
       <c r="W179" s="6" t="n"/>
       <c r="X179" s="6" t="n"/>
       <c r="Y179" s="6" t="n"/>
-      <c r="Z179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
@@ -5741,7 +5554,6 @@
       <c r="W180" s="6" t="n"/>
       <c r="X180" s="6" t="n"/>
       <c r="Y180" s="6" t="n"/>
-      <c r="Z180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
@@ -5769,7 +5581,6 @@
       <c r="W181" s="6" t="n"/>
       <c r="X181" s="6" t="n"/>
       <c r="Y181" s="6" t="n"/>
-      <c r="Z181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
@@ -5797,7 +5608,6 @@
       <c r="W182" s="6" t="n"/>
       <c r="X182" s="6" t="n"/>
       <c r="Y182" s="6" t="n"/>
-      <c r="Z182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
@@ -5825,7 +5635,6 @@
       <c r="W183" s="6" t="n"/>
       <c r="X183" s="6" t="n"/>
       <c r="Y183" s="6" t="n"/>
-      <c r="Z183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
@@ -5853,7 +5662,6 @@
       <c r="W184" s="6" t="n"/>
       <c r="X184" s="6" t="n"/>
       <c r="Y184" s="6" t="n"/>
-      <c r="Z184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
@@ -5881,7 +5689,6 @@
       <c r="W185" s="6" t="n"/>
       <c r="X185" s="6" t="n"/>
       <c r="Y185" s="6" t="n"/>
-      <c r="Z185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
@@ -5909,7 +5716,6 @@
       <c r="W186" s="6" t="n"/>
       <c r="X186" s="6" t="n"/>
       <c r="Y186" s="6" t="n"/>
-      <c r="Z186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
@@ -5937,7 +5743,6 @@
       <c r="W187" s="6" t="n"/>
       <c r="X187" s="6" t="n"/>
       <c r="Y187" s="6" t="n"/>
-      <c r="Z187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
@@ -5965,7 +5770,6 @@
       <c r="W188" s="6" t="n"/>
       <c r="X188" s="6" t="n"/>
       <c r="Y188" s="6" t="n"/>
-      <c r="Z188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
@@ -5993,7 +5797,6 @@
       <c r="W189" s="6" t="n"/>
       <c r="X189" s="6" t="n"/>
       <c r="Y189" s="6" t="n"/>
-      <c r="Z189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
@@ -6021,7 +5824,6 @@
       <c r="W190" s="6" t="n"/>
       <c r="X190" s="6" t="n"/>
       <c r="Y190" s="6" t="n"/>
-      <c r="Z190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
@@ -6049,7 +5851,6 @@
       <c r="W191" s="6" t="n"/>
       <c r="X191" s="6" t="n"/>
       <c r="Y191" s="6" t="n"/>
-      <c r="Z191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
@@ -6077,7 +5878,6 @@
       <c r="W192" s="6" t="n"/>
       <c r="X192" s="6" t="n"/>
       <c r="Y192" s="6" t="n"/>
-      <c r="Z192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
@@ -6105,7 +5905,6 @@
       <c r="W193" s="6" t="n"/>
       <c r="X193" s="6" t="n"/>
       <c r="Y193" s="6" t="n"/>
-      <c r="Z193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
@@ -6133,7 +5932,6 @@
       <c r="W194" s="6" t="n"/>
       <c r="X194" s="6" t="n"/>
       <c r="Y194" s="6" t="n"/>
-      <c r="Z194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
@@ -6161,7 +5959,6 @@
       <c r="W195" s="6" t="n"/>
       <c r="X195" s="6" t="n"/>
       <c r="Y195" s="6" t="n"/>
-      <c r="Z195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
@@ -6189,7 +5986,6 @@
       <c r="W196" s="6" t="n"/>
       <c r="X196" s="6" t="n"/>
       <c r="Y196" s="6" t="n"/>
-      <c r="Z196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
@@ -6217,7 +6013,6 @@
       <c r="W197" s="6" t="n"/>
       <c r="X197" s="6" t="n"/>
       <c r="Y197" s="6" t="n"/>
-      <c r="Z197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
@@ -6245,7 +6040,6 @@
       <c r="W198" s="6" t="n"/>
       <c r="X198" s="6" t="n"/>
       <c r="Y198" s="6" t="n"/>
-      <c r="Z198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
@@ -6273,7 +6067,6 @@
       <c r="W199" s="6" t="n"/>
       <c r="X199" s="6" t="n"/>
       <c r="Y199" s="6" t="n"/>
-      <c r="Z199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
@@ -6301,7 +6094,6 @@
       <c r="W200" s="6" t="n"/>
       <c r="X200" s="6" t="n"/>
       <c r="Y200" s="6" t="n"/>
-      <c r="Z200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
@@ -6329,7 +6121,6 @@
       <c r="W201" s="6" t="n"/>
       <c r="X201" s="6" t="n"/>
       <c r="Y201" s="6" t="n"/>
-      <c r="Z201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
@@ -6357,7 +6148,6 @@
       <c r="W202" s="6" t="n"/>
       <c r="X202" s="6" t="n"/>
       <c r="Y202" s="6" t="n"/>
-      <c r="Z202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n"/>
@@ -6385,7 +6175,6 @@
       <c r="W203" s="6" t="n"/>
       <c r="X203" s="6" t="n"/>
       <c r="Y203" s="6" t="n"/>
-      <c r="Z203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n"/>
@@ -6413,7 +6202,6 @@
       <c r="W204" s="6" t="n"/>
       <c r="X204" s="6" t="n"/>
       <c r="Y204" s="6" t="n"/>
-      <c r="Z204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n"/>
@@ -6441,7 +6229,6 @@
       <c r="W205" s="6" t="n"/>
       <c r="X205" s="6" t="n"/>
       <c r="Y205" s="6" t="n"/>
-      <c r="Z205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n"/>
@@ -6469,7 +6256,6 @@
       <c r="W206" s="6" t="n"/>
       <c r="X206" s="6" t="n"/>
       <c r="Y206" s="6" t="n"/>
-      <c r="Z206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="n"/>
@@ -6497,7 +6283,6 @@
       <c r="W207" s="6" t="n"/>
       <c r="X207" s="6" t="n"/>
       <c r="Y207" s="6" t="n"/>
-      <c r="Z207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="n"/>
@@ -6525,7 +6310,6 @@
       <c r="W208" s="6" t="n"/>
       <c r="X208" s="6" t="n"/>
       <c r="Y208" s="6" t="n"/>
-      <c r="Z208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="n"/>
@@ -6553,7 +6337,6 @@
       <c r="W209" s="6" t="n"/>
       <c r="X209" s="6" t="n"/>
       <c r="Y209" s="6" t="n"/>
-      <c r="Z209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="n"/>
@@ -6581,7 +6364,6 @@
       <c r="W210" s="6" t="n"/>
       <c r="X210" s="6" t="n"/>
       <c r="Y210" s="6" t="n"/>
-      <c r="Z210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="n"/>
@@ -6609,7 +6391,6 @@
       <c r="W211" s="6" t="n"/>
       <c r="X211" s="6" t="n"/>
       <c r="Y211" s="6" t="n"/>
-      <c r="Z211" s="6" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="n"/>
@@ -6637,7 +6418,6 @@
       <c r="W212" s="6" t="n"/>
       <c r="X212" s="6" t="n"/>
       <c r="Y212" s="6" t="n"/>
-      <c r="Z212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="n"/>
@@ -6665,7 +6445,6 @@
       <c r="W213" s="6" t="n"/>
       <c r="X213" s="6" t="n"/>
       <c r="Y213" s="6" t="n"/>
-      <c r="Z213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="n"/>
@@ -6693,7 +6472,6 @@
       <c r="W214" s="6" t="n"/>
       <c r="X214" s="6" t="n"/>
       <c r="Y214" s="6" t="n"/>
-      <c r="Z214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="n"/>
@@ -6721,7 +6499,6 @@
       <c r="W215" s="6" t="n"/>
       <c r="X215" s="6" t="n"/>
       <c r="Y215" s="6" t="n"/>
-      <c r="Z215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="n"/>
@@ -6749,7 +6526,6 @@
       <c r="W216" s="6" t="n"/>
       <c r="X216" s="6" t="n"/>
       <c r="Y216" s="6" t="n"/>
-      <c r="Z216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="n"/>
@@ -6777,7 +6553,6 @@
       <c r="W217" s="6" t="n"/>
       <c r="X217" s="6" t="n"/>
       <c r="Y217" s="6" t="n"/>
-      <c r="Z217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="n"/>
@@ -6805,7 +6580,6 @@
       <c r="W218" s="6" t="n"/>
       <c r="X218" s="6" t="n"/>
       <c r="Y218" s="6" t="n"/>
-      <c r="Z218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="n"/>
@@ -6833,7 +6607,6 @@
       <c r="W219" s="6" t="n"/>
       <c r="X219" s="6" t="n"/>
       <c r="Y219" s="6" t="n"/>
-      <c r="Z219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="n"/>
@@ -6861,7 +6634,6 @@
       <c r="W220" s="6" t="n"/>
       <c r="X220" s="6" t="n"/>
       <c r="Y220" s="6" t="n"/>
-      <c r="Z220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="n"/>
@@ -6889,7 +6661,6 @@
       <c r="W221" s="6" t="n"/>
       <c r="X221" s="6" t="n"/>
       <c r="Y221" s="6" t="n"/>
-      <c r="Z221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="n"/>
@@ -6917,7 +6688,6 @@
       <c r="W222" s="6" t="n"/>
       <c r="X222" s="6" t="n"/>
       <c r="Y222" s="6" t="n"/>
-      <c r="Z222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="n"/>
@@ -6945,7 +6715,6 @@
       <c r="W223" s="6" t="n"/>
       <c r="X223" s="6" t="n"/>
       <c r="Y223" s="6" t="n"/>
-      <c r="Z223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="n"/>
@@ -6973,7 +6742,6 @@
       <c r="W224" s="6" t="n"/>
       <c r="X224" s="6" t="n"/>
       <c r="Y224" s="6" t="n"/>
-      <c r="Z224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="n"/>
@@ -7001,7 +6769,6 @@
       <c r="W225" s="6" t="n"/>
       <c r="X225" s="6" t="n"/>
       <c r="Y225" s="6" t="n"/>
-      <c r="Z225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="n"/>
@@ -7029,7 +6796,6 @@
       <c r="W226" s="6" t="n"/>
       <c r="X226" s="6" t="n"/>
       <c r="Y226" s="6" t="n"/>
-      <c r="Z226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n"/>
@@ -7057,7 +6823,6 @@
       <c r="W227" s="6" t="n"/>
       <c r="X227" s="6" t="n"/>
       <c r="Y227" s="6" t="n"/>
-      <c r="Z227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="n"/>
@@ -7085,7 +6850,6 @@
       <c r="W228" s="6" t="n"/>
       <c r="X228" s="6" t="n"/>
       <c r="Y228" s="6" t="n"/>
-      <c r="Z228" s="6" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="n"/>
@@ -7113,7 +6877,6 @@
       <c r="W229" s="6" t="n"/>
       <c r="X229" s="6" t="n"/>
       <c r="Y229" s="6" t="n"/>
-      <c r="Z229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="n"/>
@@ -7141,7 +6904,6 @@
       <c r="W230" s="6" t="n"/>
       <c r="X230" s="6" t="n"/>
       <c r="Y230" s="6" t="n"/>
-      <c r="Z230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="n"/>
@@ -7169,7 +6931,6 @@
       <c r="W231" s="6" t="n"/>
       <c r="X231" s="6" t="n"/>
       <c r="Y231" s="6" t="n"/>
-      <c r="Z231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="n"/>
@@ -7197,7 +6958,6 @@
       <c r="W232" s="6" t="n"/>
       <c r="X232" s="6" t="n"/>
       <c r="Y232" s="6" t="n"/>
-      <c r="Z232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="n"/>
@@ -7225,7 +6985,6 @@
       <c r="W233" s="6" t="n"/>
       <c r="X233" s="6" t="n"/>
       <c r="Y233" s="6" t="n"/>
-      <c r="Z233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="n"/>
@@ -7253,7 +7012,6 @@
       <c r="W234" s="6" t="n"/>
       <c r="X234" s="6" t="n"/>
       <c r="Y234" s="6" t="n"/>
-      <c r="Z234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="n"/>
@@ -7281,7 +7039,6 @@
       <c r="W235" s="6" t="n"/>
       <c r="X235" s="6" t="n"/>
       <c r="Y235" s="6" t="n"/>
-      <c r="Z235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="n"/>
@@ -7309,7 +7066,6 @@
       <c r="W236" s="6" t="n"/>
       <c r="X236" s="6" t="n"/>
       <c r="Y236" s="6" t="n"/>
-      <c r="Z236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="n"/>
@@ -7337,7 +7093,6 @@
       <c r="W237" s="6" t="n"/>
       <c r="X237" s="6" t="n"/>
       <c r="Y237" s="6" t="n"/>
-      <c r="Z237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="n"/>
@@ -7365,7 +7120,6 @@
       <c r="W238" s="6" t="n"/>
       <c r="X238" s="6" t="n"/>
       <c r="Y238" s="6" t="n"/>
-      <c r="Z238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="n"/>
@@ -7393,7 +7147,6 @@
       <c r="W239" s="6" t="n"/>
       <c r="X239" s="6" t="n"/>
       <c r="Y239" s="6" t="n"/>
-      <c r="Z239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="n"/>
@@ -7421,7 +7174,6 @@
       <c r="W240" s="6" t="n"/>
       <c r="X240" s="6" t="n"/>
       <c r="Y240" s="6" t="n"/>
-      <c r="Z240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="n"/>
@@ -7449,7 +7201,6 @@
       <c r="W241" s="6" t="n"/>
       <c r="X241" s="6" t="n"/>
       <c r="Y241" s="6" t="n"/>
-      <c r="Z241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="n"/>
@@ -7477,7 +7228,6 @@
       <c r="W242" s="6" t="n"/>
       <c r="X242" s="6" t="n"/>
       <c r="Y242" s="6" t="n"/>
-      <c r="Z242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="n"/>
@@ -7505,7 +7255,6 @@
       <c r="W243" s="6" t="n"/>
       <c r="X243" s="6" t="n"/>
       <c r="Y243" s="6" t="n"/>
-      <c r="Z243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="n"/>
@@ -7533,7 +7282,6 @@
       <c r="W244" s="6" t="n"/>
       <c r="X244" s="6" t="n"/>
       <c r="Y244" s="6" t="n"/>
-      <c r="Z244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="n"/>
@@ -7561,7 +7309,6 @@
       <c r="W245" s="6" t="n"/>
       <c r="X245" s="6" t="n"/>
       <c r="Y245" s="6" t="n"/>
-      <c r="Z245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
@@ -7589,7 +7336,6 @@
       <c r="W246" s="6" t="n"/>
       <c r="X246" s="6" t="n"/>
       <c r="Y246" s="6" t="n"/>
-      <c r="Z246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="n"/>
@@ -7617,7 +7363,6 @@
       <c r="W247" s="6" t="n"/>
       <c r="X247" s="6" t="n"/>
       <c r="Y247" s="6" t="n"/>
-      <c r="Z247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="n"/>
@@ -7645,7 +7390,6 @@
       <c r="W248" s="6" t="n"/>
       <c r="X248" s="6" t="n"/>
       <c r="Y248" s="6" t="n"/>
-      <c r="Z248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="n"/>
@@ -7673,7 +7417,6 @@
       <c r="W249" s="6" t="n"/>
       <c r="X249" s="6" t="n"/>
       <c r="Y249" s="6" t="n"/>
-      <c r="Z249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="n"/>
@@ -7701,7 +7444,6 @@
       <c r="W250" s="6" t="n"/>
       <c r="X250" s="6" t="n"/>
       <c r="Y250" s="6" t="n"/>
-      <c r="Z250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="n"/>
@@ -7729,7 +7471,6 @@
       <c r="W251" s="6" t="n"/>
       <c r="X251" s="6" t="n"/>
       <c r="Y251" s="6" t="n"/>
-      <c r="Z251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="n"/>
@@ -7757,7 +7498,6 @@
       <c r="W252" s="6" t="n"/>
       <c r="X252" s="6" t="n"/>
       <c r="Y252" s="6" t="n"/>
-      <c r="Z252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="n"/>
@@ -7785,7 +7525,6 @@
       <c r="W253" s="6" t="n"/>
       <c r="X253" s="6" t="n"/>
       <c r="Y253" s="6" t="n"/>
-      <c r="Z253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="n"/>
@@ -7813,7 +7552,6 @@
       <c r="W254" s="6" t="n"/>
       <c r="X254" s="6" t="n"/>
       <c r="Y254" s="6" t="n"/>
-      <c r="Z254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="n"/>
@@ -7841,7 +7579,6 @@
       <c r="W255" s="6" t="n"/>
       <c r="X255" s="6" t="n"/>
       <c r="Y255" s="6" t="n"/>
-      <c r="Z255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="n"/>
@@ -7869,7 +7606,6 @@
       <c r="W256" s="6" t="n"/>
       <c r="X256" s="6" t="n"/>
       <c r="Y256" s="6" t="n"/>
-      <c r="Z256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="n"/>
@@ -7897,7 +7633,6 @@
       <c r="W257" s="6" t="n"/>
       <c r="X257" s="6" t="n"/>
       <c r="Y257" s="6" t="n"/>
-      <c r="Z257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="n"/>
@@ -7925,7 +7660,6 @@
       <c r="W258" s="6" t="n"/>
       <c r="X258" s="6" t="n"/>
       <c r="Y258" s="6" t="n"/>
-      <c r="Z258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="n"/>
@@ -7953,7 +7687,6 @@
       <c r="W259" s="6" t="n"/>
       <c r="X259" s="6" t="n"/>
       <c r="Y259" s="6" t="n"/>
-      <c r="Z259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="n"/>
@@ -7981,7 +7714,6 @@
       <c r="W260" s="6" t="n"/>
       <c r="X260" s="6" t="n"/>
       <c r="Y260" s="6" t="n"/>
-      <c r="Z260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="n"/>
@@ -8009,7 +7741,6 @@
       <c r="W261" s="6" t="n"/>
       <c r="X261" s="6" t="n"/>
       <c r="Y261" s="6" t="n"/>
-      <c r="Z261" s="6" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="n"/>
@@ -8037,7 +7768,6 @@
       <c r="W262" s="6" t="n"/>
       <c r="X262" s="6" t="n"/>
       <c r="Y262" s="6" t="n"/>
-      <c r="Z262" s="6" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="n"/>
@@ -8065,7 +7795,6 @@
       <c r="W263" s="6" t="n"/>
       <c r="X263" s="6" t="n"/>
       <c r="Y263" s="6" t="n"/>
-      <c r="Z263" s="6" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="n"/>
@@ -8093,7 +7822,6 @@
       <c r="W264" s="6" t="n"/>
       <c r="X264" s="6" t="n"/>
       <c r="Y264" s="6" t="n"/>
-      <c r="Z264" s="6" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="n"/>
@@ -8121,7 +7849,6 @@
       <c r="W265" s="6" t="n"/>
       <c r="X265" s="6" t="n"/>
       <c r="Y265" s="6" t="n"/>
-      <c r="Z265" s="6" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="n"/>
@@ -8149,7 +7876,6 @@
       <c r="W266" s="6" t="n"/>
       <c r="X266" s="6" t="n"/>
       <c r="Y266" s="6" t="n"/>
-      <c r="Z266" s="6" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="n"/>
@@ -8177,7 +7903,6 @@
       <c r="W267" s="6" t="n"/>
       <c r="X267" s="6" t="n"/>
       <c r="Y267" s="6" t="n"/>
-      <c r="Z267" s="6" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="n"/>
@@ -8205,7 +7930,6 @@
       <c r="W268" s="6" t="n"/>
       <c r="X268" s="6" t="n"/>
       <c r="Y268" s="6" t="n"/>
-      <c r="Z268" s="6" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="n"/>
@@ -8233,7 +7957,6 @@
       <c r="W269" s="6" t="n"/>
       <c r="X269" s="6" t="n"/>
       <c r="Y269" s="6" t="n"/>
-      <c r="Z269" s="6" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="n"/>
@@ -8261,7 +7984,6 @@
       <c r="W270" s="6" t="n"/>
       <c r="X270" s="6" t="n"/>
       <c r="Y270" s="6" t="n"/>
-      <c r="Z270" s="6" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="n"/>
@@ -8289,7 +8011,6 @@
       <c r="W271" s="6" t="n"/>
       <c r="X271" s="6" t="n"/>
       <c r="Y271" s="6" t="n"/>
-      <c r="Z271" s="6" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="n"/>
@@ -8317,7 +8038,6 @@
       <c r="W272" s="6" t="n"/>
       <c r="X272" s="6" t="n"/>
       <c r="Y272" s="6" t="n"/>
-      <c r="Z272" s="6" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="n"/>
@@ -8345,7 +8065,6 @@
       <c r="W273" s="6" t="n"/>
       <c r="X273" s="6" t="n"/>
       <c r="Y273" s="6" t="n"/>
-      <c r="Z273" s="6" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="n"/>
@@ -8373,7 +8092,6 @@
       <c r="W274" s="6" t="n"/>
       <c r="X274" s="6" t="n"/>
       <c r="Y274" s="6" t="n"/>
-      <c r="Z274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="n"/>
@@ -8401,7 +8119,6 @@
       <c r="W275" s="6" t="n"/>
       <c r="X275" s="6" t="n"/>
       <c r="Y275" s="6" t="n"/>
-      <c r="Z275" s="6" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="n"/>
@@ -8429,7 +8146,6 @@
       <c r="W276" s="6" t="n"/>
       <c r="X276" s="6" t="n"/>
       <c r="Y276" s="6" t="n"/>
-      <c r="Z276" s="6" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="n"/>
@@ -8457,7 +8173,6 @@
       <c r="W277" s="6" t="n"/>
       <c r="X277" s="6" t="n"/>
       <c r="Y277" s="6" t="n"/>
-      <c r="Z277" s="6" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="n"/>
@@ -8485,7 +8200,6 @@
       <c r="W278" s="6" t="n"/>
       <c r="X278" s="6" t="n"/>
       <c r="Y278" s="6" t="n"/>
-      <c r="Z278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n"/>
@@ -8513,7 +8227,6 @@
       <c r="W279" s="6" t="n"/>
       <c r="X279" s="6" t="n"/>
       <c r="Y279" s="6" t="n"/>
-      <c r="Z279" s="6" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="n"/>
@@ -8541,7 +8254,6 @@
       <c r="W280" s="6" t="n"/>
       <c r="X280" s="6" t="n"/>
       <c r="Y280" s="6" t="n"/>
-      <c r="Z280" s="6" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="n"/>
@@ -8569,7 +8281,6 @@
       <c r="W281" s="6" t="n"/>
       <c r="X281" s="6" t="n"/>
       <c r="Y281" s="6" t="n"/>
-      <c r="Z281" s="6" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="n"/>
@@ -8597,7 +8308,6 @@
       <c r="W282" s="6" t="n"/>
       <c r="X282" s="6" t="n"/>
       <c r="Y282" s="6" t="n"/>
-      <c r="Z282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="n"/>
@@ -8625,7 +8335,6 @@
       <c r="W283" s="6" t="n"/>
       <c r="X283" s="6" t="n"/>
       <c r="Y283" s="6" t="n"/>
-      <c r="Z283" s="6" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="n"/>
@@ -8653,7 +8362,6 @@
       <c r="W284" s="6" t="n"/>
       <c r="X284" s="6" t="n"/>
       <c r="Y284" s="6" t="n"/>
-      <c r="Z284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="n"/>
@@ -8681,7 +8389,6 @@
       <c r="W285" s="6" t="n"/>
       <c r="X285" s="6" t="n"/>
       <c r="Y285" s="6" t="n"/>
-      <c r="Z285" s="6" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="n"/>
@@ -8709,7 +8416,6 @@
       <c r="W286" s="6" t="n"/>
       <c r="X286" s="6" t="n"/>
       <c r="Y286" s="6" t="n"/>
-      <c r="Z286" s="6" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="n"/>
@@ -8737,7 +8443,6 @@
       <c r="W287" s="6" t="n"/>
       <c r="X287" s="6" t="n"/>
       <c r="Y287" s="6" t="n"/>
-      <c r="Z287" s="6" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="n"/>
@@ -8765,7 +8470,6 @@
       <c r="W288" s="6" t="n"/>
       <c r="X288" s="6" t="n"/>
       <c r="Y288" s="6" t="n"/>
-      <c r="Z288" s="6" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="n"/>
@@ -8793,7 +8497,6 @@
       <c r="W289" s="6" t="n"/>
       <c r="X289" s="6" t="n"/>
       <c r="Y289" s="6" t="n"/>
-      <c r="Z289" s="6" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="n"/>
@@ -8821,7 +8524,6 @@
       <c r="W290" s="6" t="n"/>
       <c r="X290" s="6" t="n"/>
       <c r="Y290" s="6" t="n"/>
-      <c r="Z290" s="6" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="n"/>
@@ -8849,7 +8551,6 @@
       <c r="W291" s="6" t="n"/>
       <c r="X291" s="6" t="n"/>
       <c r="Y291" s="6" t="n"/>
-      <c r="Z291" s="6" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="n"/>
@@ -8877,7 +8578,6 @@
       <c r="W292" s="6" t="n"/>
       <c r="X292" s="6" t="n"/>
       <c r="Y292" s="6" t="n"/>
-      <c r="Z292" s="6" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="n"/>
@@ -8905,7 +8605,6 @@
       <c r="W293" s="6" t="n"/>
       <c r="X293" s="6" t="n"/>
       <c r="Y293" s="6" t="n"/>
-      <c r="Z293" s="6" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="n"/>
@@ -8933,7 +8632,6 @@
       <c r="W294" s="6" t="n"/>
       <c r="X294" s="6" t="n"/>
       <c r="Y294" s="6" t="n"/>
-      <c r="Z294" s="6" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="n"/>
@@ -8961,7 +8659,6 @@
       <c r="W295" s="6" t="n"/>
       <c r="X295" s="6" t="n"/>
       <c r="Y295" s="6" t="n"/>
-      <c r="Z295" s="6" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="n"/>
@@ -8989,7 +8686,6 @@
       <c r="W296" s="6" t="n"/>
       <c r="X296" s="6" t="n"/>
       <c r="Y296" s="6" t="n"/>
-      <c r="Z296" s="6" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="n"/>
@@ -9017,7 +8713,6 @@
       <c r="W297" s="6" t="n"/>
       <c r="X297" s="6" t="n"/>
       <c r="Y297" s="6" t="n"/>
-      <c r="Z297" s="6" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="n"/>
@@ -9045,7 +8740,6 @@
       <c r="W298" s="6" t="n"/>
       <c r="X298" s="6" t="n"/>
       <c r="Y298" s="6" t="n"/>
-      <c r="Z298" s="6" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="n"/>
@@ -9073,7 +8767,6 @@
       <c r="W299" s="6" t="n"/>
       <c r="X299" s="6" t="n"/>
       <c r="Y299" s="6" t="n"/>
-      <c r="Z299" s="6" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="n"/>
@@ -9101,7 +8794,6 @@
       <c r="W300" s="6" t="n"/>
       <c r="X300" s="6" t="n"/>
       <c r="Y300" s="6" t="n"/>
-      <c r="Z300" s="6" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="n"/>
@@ -9129,7 +8821,6 @@
       <c r="W301" s="6" t="n"/>
       <c r="X301" s="6" t="n"/>
       <c r="Y301" s="6" t="n"/>
-      <c r="Z301" s="6" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="n"/>
@@ -9157,7 +8848,6 @@
       <c r="W302" s="6" t="n"/>
       <c r="X302" s="6" t="n"/>
       <c r="Y302" s="6" t="n"/>
-      <c r="Z302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="6" t="n"/>
@@ -9185,7 +8875,6 @@
       <c r="W303" s="6" t="n"/>
       <c r="X303" s="6" t="n"/>
       <c r="Y303" s="6" t="n"/>
-      <c r="Z303" s="6" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="6" t="n"/>
@@ -9213,7 +8902,6 @@
       <c r="W304" s="6" t="n"/>
       <c r="X304" s="6" t="n"/>
       <c r="Y304" s="6" t="n"/>
-      <c r="Z304" s="6" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="6" t="n"/>
@@ -9241,7 +8929,6 @@
       <c r="W305" s="6" t="n"/>
       <c r="X305" s="6" t="n"/>
       <c r="Y305" s="6" t="n"/>
-      <c r="Z305" s="6" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="6" t="n"/>
@@ -9269,7 +8956,6 @@
       <c r="W306" s="6" t="n"/>
       <c r="X306" s="6" t="n"/>
       <c r="Y306" s="6" t="n"/>
-      <c r="Z306" s="6" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="6" t="n"/>
@@ -9297,7 +8983,6 @@
       <c r="W307" s="6" t="n"/>
       <c r="X307" s="6" t="n"/>
       <c r="Y307" s="6" t="n"/>
-      <c r="Z307" s="6" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="6" t="n"/>
@@ -9325,7 +9010,6 @@
       <c r="W308" s="6" t="n"/>
       <c r="X308" s="6" t="n"/>
       <c r="Y308" s="6" t="n"/>
-      <c r="Z308" s="6" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="n"/>
@@ -9353,7 +9037,6 @@
       <c r="W309" s="6" t="n"/>
       <c r="X309" s="6" t="n"/>
       <c r="Y309" s="6" t="n"/>
-      <c r="Z309" s="6" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="6" t="n"/>
@@ -9381,7 +9064,6 @@
       <c r="W310" s="6" t="n"/>
       <c r="X310" s="6" t="n"/>
       <c r="Y310" s="6" t="n"/>
-      <c r="Z310" s="6" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="6" t="n"/>
@@ -9409,7 +9091,6 @@
       <c r="W311" s="6" t="n"/>
       <c r="X311" s="6" t="n"/>
       <c r="Y311" s="6" t="n"/>
-      <c r="Z311" s="6" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="6" t="n"/>
@@ -9437,7 +9118,6 @@
       <c r="W312" s="6" t="n"/>
       <c r="X312" s="6" t="n"/>
       <c r="Y312" s="6" t="n"/>
-      <c r="Z312" s="6" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="6" t="n"/>
@@ -9465,7 +9145,6 @@
       <c r="W313" s="6" t="n"/>
       <c r="X313" s="6" t="n"/>
       <c r="Y313" s="6" t="n"/>
-      <c r="Z313" s="6" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="6" t="n"/>
@@ -9493,7 +9172,6 @@
       <c r="W314" s="6" t="n"/>
       <c r="X314" s="6" t="n"/>
       <c r="Y314" s="6" t="n"/>
-      <c r="Z314" s="6" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="6" t="n"/>
@@ -9521,7 +9199,6 @@
       <c r="W315" s="6" t="n"/>
       <c r="X315" s="6" t="n"/>
       <c r="Y315" s="6" t="n"/>
-      <c r="Z315" s="6" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="6" t="n"/>
@@ -9549,7 +9226,6 @@
       <c r="W316" s="6" t="n"/>
       <c r="X316" s="6" t="n"/>
       <c r="Y316" s="6" t="n"/>
-      <c r="Z316" s="6" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="6" t="n"/>
@@ -9577,7 +9253,6 @@
       <c r="W317" s="6" t="n"/>
       <c r="X317" s="6" t="n"/>
       <c r="Y317" s="6" t="n"/>
-      <c r="Z317" s="6" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="6" t="n"/>
@@ -9605,7 +9280,6 @@
       <c r="W318" s="6" t="n"/>
       <c r="X318" s="6" t="n"/>
       <c r="Y318" s="6" t="n"/>
-      <c r="Z318" s="6" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="6" t="n"/>
@@ -9633,7 +9307,6 @@
       <c r="W319" s="6" t="n"/>
       <c r="X319" s="6" t="n"/>
       <c r="Y319" s="6" t="n"/>
-      <c r="Z319" s="6" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="6" t="n"/>
@@ -9661,7 +9334,6 @@
       <c r="W320" s="6" t="n"/>
       <c r="X320" s="6" t="n"/>
       <c r="Y320" s="6" t="n"/>
-      <c r="Z320" s="6" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="6" t="n"/>
@@ -9689,7 +9361,6 @@
       <c r="W321" s="6" t="n"/>
       <c r="X321" s="6" t="n"/>
       <c r="Y321" s="6" t="n"/>
-      <c r="Z321" s="6" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="6" t="n"/>
@@ -9717,7 +9388,6 @@
       <c r="W322" s="6" t="n"/>
       <c r="X322" s="6" t="n"/>
       <c r="Y322" s="6" t="n"/>
-      <c r="Z322" s="6" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="n"/>
@@ -9745,7 +9415,6 @@
       <c r="W323" s="6" t="n"/>
       <c r="X323" s="6" t="n"/>
       <c r="Y323" s="6" t="n"/>
-      <c r="Z323" s="6" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="6" t="n"/>
@@ -9773,7 +9442,6 @@
       <c r="W324" s="6" t="n"/>
       <c r="X324" s="6" t="n"/>
       <c r="Y324" s="6" t="n"/>
-      <c r="Z324" s="6" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="6" t="n"/>
@@ -9801,7 +9469,6 @@
       <c r="W325" s="6" t="n"/>
       <c r="X325" s="6" t="n"/>
       <c r="Y325" s="6" t="n"/>
-      <c r="Z325" s="6" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="6" t="n"/>
@@ -9829,7 +9496,6 @@
       <c r="W326" s="6" t="n"/>
       <c r="X326" s="6" t="n"/>
       <c r="Y326" s="6" t="n"/>
-      <c r="Z326" s="6" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="6" t="n"/>
@@ -9857,7 +9523,6 @@
       <c r="W327" s="6" t="n"/>
       <c r="X327" s="6" t="n"/>
       <c r="Y327" s="6" t="n"/>
-      <c r="Z327" s="6" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="6" t="n"/>
@@ -9885,7 +9550,6 @@
       <c r="W328" s="6" t="n"/>
       <c r="X328" s="6" t="n"/>
       <c r="Y328" s="6" t="n"/>
-      <c r="Z328" s="6" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="6" t="n"/>
@@ -9913,7 +9577,6 @@
       <c r="W329" s="6" t="n"/>
       <c r="X329" s="6" t="n"/>
       <c r="Y329" s="6" t="n"/>
-      <c r="Z329" s="6" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="6" t="n"/>
@@ -9941,7 +9604,6 @@
       <c r="W330" s="6" t="n"/>
       <c r="X330" s="6" t="n"/>
       <c r="Y330" s="6" t="n"/>
-      <c r="Z330" s="6" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="6" t="n"/>
@@ -9969,7 +9631,6 @@
       <c r="W331" s="6" t="n"/>
       <c r="X331" s="6" t="n"/>
       <c r="Y331" s="6" t="n"/>
-      <c r="Z331" s="6" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="6" t="n"/>
@@ -9997,7 +9658,6 @@
       <c r="W332" s="6" t="n"/>
       <c r="X332" s="6" t="n"/>
       <c r="Y332" s="6" t="n"/>
-      <c r="Z332" s="6" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="6" t="n"/>
@@ -10025,7 +9685,6 @@
       <c r="W333" s="6" t="n"/>
       <c r="X333" s="6" t="n"/>
       <c r="Y333" s="6" t="n"/>
-      <c r="Z333" s="6" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="6" t="n"/>
@@ -10053,7 +9712,6 @@
       <c r="W334" s="6" t="n"/>
       <c r="X334" s="6" t="n"/>
       <c r="Y334" s="6" t="n"/>
-      <c r="Z334" s="6" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="6" t="n"/>
@@ -10081,7 +9739,6 @@
       <c r="W335" s="6" t="n"/>
       <c r="X335" s="6" t="n"/>
       <c r="Y335" s="6" t="n"/>
-      <c r="Z335" s="6" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="6" t="n"/>
@@ -10109,7 +9766,6 @@
       <c r="W336" s="6" t="n"/>
       <c r="X336" s="6" t="n"/>
       <c r="Y336" s="6" t="n"/>
-      <c r="Z336" s="6" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="n"/>
@@ -10137,7 +9793,6 @@
       <c r="W337" s="6" t="n"/>
       <c r="X337" s="6" t="n"/>
       <c r="Y337" s="6" t="n"/>
-      <c r="Z337" s="6" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="6" t="n"/>
@@ -10165,7 +9820,6 @@
       <c r="W338" s="6" t="n"/>
       <c r="X338" s="6" t="n"/>
       <c r="Y338" s="6" t="n"/>
-      <c r="Z338" s="6" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="6" t="n"/>
@@ -10193,7 +9847,6 @@
       <c r="W339" s="6" t="n"/>
       <c r="X339" s="6" t="n"/>
       <c r="Y339" s="6" t="n"/>
-      <c r="Z339" s="6" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="6" t="n"/>
@@ -10221,7 +9874,6 @@
       <c r="W340" s="6" t="n"/>
       <c r="X340" s="6" t="n"/>
       <c r="Y340" s="6" t="n"/>
-      <c r="Z340" s="6" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="6" t="n"/>
@@ -10249,7 +9901,6 @@
       <c r="W341" s="6" t="n"/>
       <c r="X341" s="6" t="n"/>
       <c r="Y341" s="6" t="n"/>
-      <c r="Z341" s="6" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="6" t="n"/>
@@ -10277,7 +9928,6 @@
       <c r="W342" s="6" t="n"/>
       <c r="X342" s="6" t="n"/>
       <c r="Y342" s="6" t="n"/>
-      <c r="Z342" s="6" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="n"/>
@@ -10305,7 +9955,6 @@
       <c r="W343" s="6" t="n"/>
       <c r="X343" s="6" t="n"/>
       <c r="Y343" s="6" t="n"/>
-      <c r="Z343" s="6" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="6" t="n"/>
@@ -10333,7 +9982,6 @@
       <c r="W344" s="6" t="n"/>
       <c r="X344" s="6" t="n"/>
       <c r="Y344" s="6" t="n"/>
-      <c r="Z344" s="6" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="6" t="n"/>
@@ -10361,7 +10009,6 @@
       <c r="W345" s="6" t="n"/>
       <c r="X345" s="6" t="n"/>
       <c r="Y345" s="6" t="n"/>
-      <c r="Z345" s="6" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="6" t="n"/>
@@ -10389,7 +10036,6 @@
       <c r="W346" s="6" t="n"/>
       <c r="X346" s="6" t="n"/>
       <c r="Y346" s="6" t="n"/>
-      <c r="Z346" s="6" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="6" t="n"/>
@@ -10417,7 +10063,6 @@
       <c r="W347" s="6" t="n"/>
       <c r="X347" s="6" t="n"/>
       <c r="Y347" s="6" t="n"/>
-      <c r="Z347" s="6" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="6" t="n"/>
@@ -10445,7 +10090,6 @@
       <c r="W348" s="6" t="n"/>
       <c r="X348" s="6" t="n"/>
       <c r="Y348" s="6" t="n"/>
-      <c r="Z348" s="6" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="6" t="n"/>
@@ -10473,7 +10117,6 @@
       <c r="W349" s="6" t="n"/>
       <c r="X349" s="6" t="n"/>
       <c r="Y349" s="6" t="n"/>
-      <c r="Z349" s="6" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="6" t="n"/>
@@ -10501,7 +10144,6 @@
       <c r="W350" s="6" t="n"/>
       <c r="X350" s="6" t="n"/>
       <c r="Y350" s="6" t="n"/>
-      <c r="Z350" s="6" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="n"/>
@@ -10529,7 +10171,6 @@
       <c r="W351" s="6" t="n"/>
       <c r="X351" s="6" t="n"/>
       <c r="Y351" s="6" t="n"/>
-      <c r="Z351" s="6" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="6" t="n"/>
@@ -10557,7 +10198,6 @@
       <c r="W352" s="6" t="n"/>
       <c r="X352" s="6" t="n"/>
       <c r="Y352" s="6" t="n"/>
-      <c r="Z352" s="6" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="6" t="n"/>
@@ -10585,7 +10225,6 @@
       <c r="W353" s="6" t="n"/>
       <c r="X353" s="6" t="n"/>
       <c r="Y353" s="6" t="n"/>
-      <c r="Z353" s="6" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="6" t="n"/>
@@ -10613,7 +10252,6 @@
       <c r="W354" s="6" t="n"/>
       <c r="X354" s="6" t="n"/>
       <c r="Y354" s="6" t="n"/>
-      <c r="Z354" s="6" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="6" t="n"/>
@@ -10641,7 +10279,6 @@
       <c r="W355" s="6" t="n"/>
       <c r="X355" s="6" t="n"/>
       <c r="Y355" s="6" t="n"/>
-      <c r="Z355" s="6" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="6" t="n"/>
@@ -10669,7 +10306,6 @@
       <c r="W356" s="6" t="n"/>
       <c r="X356" s="6" t="n"/>
       <c r="Y356" s="6" t="n"/>
-      <c r="Z356" s="6" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="n"/>
@@ -10697,7 +10333,6 @@
       <c r="W357" s="6" t="n"/>
       <c r="X357" s="6" t="n"/>
       <c r="Y357" s="6" t="n"/>
-      <c r="Z357" s="6" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="n"/>
@@ -10725,7 +10360,6 @@
       <c r="W358" s="6" t="n"/>
       <c r="X358" s="6" t="n"/>
       <c r="Y358" s="6" t="n"/>
-      <c r="Z358" s="6" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="6" t="n"/>
@@ -10753,7 +10387,6 @@
       <c r="W359" s="6" t="n"/>
       <c r="X359" s="6" t="n"/>
       <c r="Y359" s="6" t="n"/>
-      <c r="Z359" s="6" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="6" t="n"/>
@@ -10781,7 +10414,6 @@
       <c r="W360" s="6" t="n"/>
       <c r="X360" s="6" t="n"/>
       <c r="Y360" s="6" t="n"/>
-      <c r="Z360" s="6" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="6" t="n"/>
@@ -10809,7 +10441,6 @@
       <c r="W361" s="6" t="n"/>
       <c r="X361" s="6" t="n"/>
       <c r="Y361" s="6" t="n"/>
-      <c r="Z361" s="6" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="6" t="n"/>
@@ -10837,7 +10468,6 @@
       <c r="W362" s="6" t="n"/>
       <c r="X362" s="6" t="n"/>
       <c r="Y362" s="6" t="n"/>
-      <c r="Z362" s="6" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="6" t="n"/>
@@ -10865,7 +10495,6 @@
       <c r="W363" s="6" t="n"/>
       <c r="X363" s="6" t="n"/>
       <c r="Y363" s="6" t="n"/>
-      <c r="Z363" s="6" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="6" t="n"/>
@@ -10893,7 +10522,6 @@
       <c r="W364" s="6" t="n"/>
       <c r="X364" s="6" t="n"/>
       <c r="Y364" s="6" t="n"/>
-      <c r="Z364" s="6" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="n"/>
@@ -10921,7 +10549,6 @@
       <c r="W365" s="6" t="n"/>
       <c r="X365" s="6" t="n"/>
       <c r="Y365" s="6" t="n"/>
-      <c r="Z365" s="6" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="6" t="n"/>
@@ -10949,7 +10576,6 @@
       <c r="W366" s="6" t="n"/>
       <c r="X366" s="6" t="n"/>
       <c r="Y366" s="6" t="n"/>
-      <c r="Z366" s="6" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="6" t="n"/>
@@ -10977,7 +10603,6 @@
       <c r="W367" s="6" t="n"/>
       <c r="X367" s="6" t="n"/>
       <c r="Y367" s="6" t="n"/>
-      <c r="Z367" s="6" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="6" t="n"/>
@@ -11005,7 +10630,6 @@
       <c r="W368" s="6" t="n"/>
       <c r="X368" s="6" t="n"/>
       <c r="Y368" s="6" t="n"/>
-      <c r="Z368" s="6" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="6" t="n"/>
@@ -11033,7 +10657,6 @@
       <c r="W369" s="6" t="n"/>
       <c r="X369" s="6" t="n"/>
       <c r="Y369" s="6" t="n"/>
-      <c r="Z369" s="6" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="6" t="n"/>
@@ -11061,7 +10684,6 @@
       <c r="W370" s="6" t="n"/>
       <c r="X370" s="6" t="n"/>
       <c r="Y370" s="6" t="n"/>
-      <c r="Z370" s="6" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="n"/>
@@ -11089,7 +10711,6 @@
       <c r="W371" s="6" t="n"/>
       <c r="X371" s="6" t="n"/>
       <c r="Y371" s="6" t="n"/>
-      <c r="Z371" s="6" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="6" t="n"/>
@@ -11117,7 +10738,6 @@
       <c r="W372" s="6" t="n"/>
       <c r="X372" s="6" t="n"/>
       <c r="Y372" s="6" t="n"/>
-      <c r="Z372" s="6" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="6" t="n"/>
@@ -11145,7 +10765,6 @@
       <c r="W373" s="6" t="n"/>
       <c r="X373" s="6" t="n"/>
       <c r="Y373" s="6" t="n"/>
-      <c r="Z373" s="6" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="6" t="n"/>
@@ -11173,7 +10792,6 @@
       <c r="W374" s="6" t="n"/>
       <c r="X374" s="6" t="n"/>
       <c r="Y374" s="6" t="n"/>
-      <c r="Z374" s="6" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="6" t="n"/>
@@ -11201,7 +10819,6 @@
       <c r="W375" s="6" t="n"/>
       <c r="X375" s="6" t="n"/>
       <c r="Y375" s="6" t="n"/>
-      <c r="Z375" s="6" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="6" t="n"/>
@@ -11229,7 +10846,6 @@
       <c r="W376" s="6" t="n"/>
       <c r="X376" s="6" t="n"/>
       <c r="Y376" s="6" t="n"/>
-      <c r="Z376" s="6" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="6" t="n"/>
@@ -11257,7 +10873,6 @@
       <c r="W377" s="6" t="n"/>
       <c r="X377" s="6" t="n"/>
       <c r="Y377" s="6" t="n"/>
-      <c r="Z377" s="6" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="6" t="n"/>
@@ -11285,7 +10900,6 @@
       <c r="W378" s="6" t="n"/>
       <c r="X378" s="6" t="n"/>
       <c r="Y378" s="6" t="n"/>
-      <c r="Z378" s="6" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="n"/>
@@ -11313,7 +10927,6 @@
       <c r="W379" s="6" t="n"/>
       <c r="X379" s="6" t="n"/>
       <c r="Y379" s="6" t="n"/>
-      <c r="Z379" s="6" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="6" t="n"/>
@@ -11341,7 +10954,6 @@
       <c r="W380" s="6" t="n"/>
       <c r="X380" s="6" t="n"/>
       <c r="Y380" s="6" t="n"/>
-      <c r="Z380" s="6" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="6" t="n"/>
@@ -11369,7 +10981,6 @@
       <c r="W381" s="6" t="n"/>
       <c r="X381" s="6" t="n"/>
       <c r="Y381" s="6" t="n"/>
-      <c r="Z381" s="6" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="6" t="n"/>
@@ -11397,7 +11008,6 @@
       <c r="W382" s="6" t="n"/>
       <c r="X382" s="6" t="n"/>
       <c r="Y382" s="6" t="n"/>
-      <c r="Z382" s="6" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="6" t="n"/>
@@ -11425,7 +11035,6 @@
       <c r="W383" s="6" t="n"/>
       <c r="X383" s="6" t="n"/>
       <c r="Y383" s="6" t="n"/>
-      <c r="Z383" s="6" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="6" t="n"/>
@@ -11453,7 +11062,6 @@
       <c r="W384" s="6" t="n"/>
       <c r="X384" s="6" t="n"/>
       <c r="Y384" s="6" t="n"/>
-      <c r="Z384" s="6" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="n"/>
@@ -11481,7 +11089,6 @@
       <c r="W385" s="6" t="n"/>
       <c r="X385" s="6" t="n"/>
       <c r="Y385" s="6" t="n"/>
-      <c r="Z385" s="6" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="6" t="n"/>
@@ -11509,7 +11116,6 @@
       <c r="W386" s="6" t="n"/>
       <c r="X386" s="6" t="n"/>
       <c r="Y386" s="6" t="n"/>
-      <c r="Z386" s="6" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="6" t="n"/>
@@ -11537,7 +11143,6 @@
       <c r="W387" s="6" t="n"/>
       <c r="X387" s="6" t="n"/>
       <c r="Y387" s="6" t="n"/>
-      <c r="Z387" s="6" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="6" t="n"/>
@@ -11565,7 +11170,6 @@
       <c r="W388" s="6" t="n"/>
       <c r="X388" s="6" t="n"/>
       <c r="Y388" s="6" t="n"/>
-      <c r="Z388" s="6" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="6" t="n"/>
@@ -11593,7 +11197,6 @@
       <c r="W389" s="6" t="n"/>
       <c r="X389" s="6" t="n"/>
       <c r="Y389" s="6" t="n"/>
-      <c r="Z389" s="6" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="6" t="n"/>
@@ -11621,7 +11224,6 @@
       <c r="W390" s="6" t="n"/>
       <c r="X390" s="6" t="n"/>
       <c r="Y390" s="6" t="n"/>
-      <c r="Z390" s="6" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="6" t="n"/>
@@ -11649,7 +11251,6 @@
       <c r="W391" s="6" t="n"/>
       <c r="X391" s="6" t="n"/>
       <c r="Y391" s="6" t="n"/>
-      <c r="Z391" s="6" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="6" t="n"/>
@@ -11677,7 +11278,6 @@
       <c r="W392" s="6" t="n"/>
       <c r="X392" s="6" t="n"/>
       <c r="Y392" s="6" t="n"/>
-      <c r="Z392" s="6" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="6" t="n"/>
@@ -11705,7 +11305,6 @@
       <c r="W393" s="6" t="n"/>
       <c r="X393" s="6" t="n"/>
       <c r="Y393" s="6" t="n"/>
-      <c r="Z393" s="6" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="6" t="n"/>
@@ -11733,7 +11332,6 @@
       <c r="W394" s="6" t="n"/>
       <c r="X394" s="6" t="n"/>
       <c r="Y394" s="6" t="n"/>
-      <c r="Z394" s="6" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="6" t="n"/>
@@ -11761,7 +11359,6 @@
       <c r="W395" s="6" t="n"/>
       <c r="X395" s="6" t="n"/>
       <c r="Y395" s="6" t="n"/>
-      <c r="Z395" s="6" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="6" t="n"/>
@@ -11789,7 +11386,6 @@
       <c r="W396" s="6" t="n"/>
       <c r="X396" s="6" t="n"/>
       <c r="Y396" s="6" t="n"/>
-      <c r="Z396" s="6" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="6" t="n"/>
@@ -11817,7 +11413,6 @@
       <c r="W397" s="6" t="n"/>
       <c r="X397" s="6" t="n"/>
       <c r="Y397" s="6" t="n"/>
-      <c r="Z397" s="6" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="6" t="n"/>
@@ -11845,7 +11440,6 @@
       <c r="W398" s="6" t="n"/>
       <c r="X398" s="6" t="n"/>
       <c r="Y398" s="6" t="n"/>
-      <c r="Z398" s="6" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="n"/>
@@ -11873,7 +11467,6 @@
       <c r="W399" s="6" t="n"/>
       <c r="X399" s="6" t="n"/>
       <c r="Y399" s="6" t="n"/>
-      <c r="Z399" s="6" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="6" t="n"/>
@@ -11901,7 +11494,6 @@
       <c r="W400" s="6" t="n"/>
       <c r="X400" s="6" t="n"/>
       <c r="Y400" s="6" t="n"/>
-      <c r="Z400" s="6" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="6" t="n"/>
@@ -11929,7 +11521,6 @@
       <c r="W401" s="6" t="n"/>
       <c r="X401" s="6" t="n"/>
       <c r="Y401" s="6" t="n"/>
-      <c r="Z401" s="6" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="6" t="n"/>
@@ -11957,7 +11548,6 @@
       <c r="W402" s="6" t="n"/>
       <c r="X402" s="6" t="n"/>
       <c r="Y402" s="6" t="n"/>
-      <c r="Z402" s="6" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="6" t="n"/>
@@ -11985,7 +11575,6 @@
       <c r="W403" s="6" t="n"/>
       <c r="X403" s="6" t="n"/>
       <c r="Y403" s="6" t="n"/>
-      <c r="Z403" s="6" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="6" t="n"/>
@@ -12013,7 +11602,6 @@
       <c r="W404" s="6" t="n"/>
       <c r="X404" s="6" t="n"/>
       <c r="Y404" s="6" t="n"/>
-      <c r="Z404" s="6" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="6" t="n"/>
@@ -12041,24 +11629,20 @@
       <c r="W405" s="6" t="n"/>
       <c r="X405" s="6" t="n"/>
       <c r="Y405" s="6" t="n"/>
-      <c r="Z405" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:Y1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="C4:C406" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Kelas tidak valid" error="Pilih salah satu kelas dari daftar." type="list">
       <formula1>"1A,1B,1C,2A,2B,3A,3B,3C,4A,4B,5A,5B,5C,6A,6B"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4:D406" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Iqro,Al-Quran,"</formula1>
+    <dataValidation sqref="G4:G406" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Aktif,Nonaktif,"</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H406" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Aktif,Nonaktif,"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I4:I406" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Laki-laki,Perempuan,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12121,63 +11705,58 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>•  Template ini TIDAK mencakup data Tahsin-Tahfizh (jenjang Iqro/Al-Qur'an, dsb) — itu bukan urusan admin lewat fitur ini, dan dikelola tersendiri oleh guru Tahsin-Tahfizh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Kolom</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>NIS</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Nomor Induk Siswa. Kosongkan atau isi "-" kalau belum tahu. WAJIB unik — jangan ada dua baris dengan NIS yang sama.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Nama Lengkap *</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Nama lengkap siswa sesuai akta/dokumen resmi.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Kelas *</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Salah satu dari: 1A, 1B, 1C, 2A, 2B, 3A, 3B, 3C, 4A, 4B, 5A, 5B, 5C, 6A, 6B. Pilih lewat dropdown supaya tidak salah ketik.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Jenjang Tahsin-Tahfizh</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Iqro atau Al-Quran. Kosongkan kalau belum tahu — sistem akan menebak dari kelas (kelas 1-2 = Iqro, lainnya = Al-Quran) khusus untuk siswa BARU; siswa yang sudah ada datanya tidak akan diubah kalau kolom ini dikosongkan.</t>
         </is>
       </c>
     </row>
@@ -12386,11 +11965,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:B6"/>
   </mergeCells>
